--- a/public/docs/ImportAssetTemplate.xlsx
+++ b/public/docs/ImportAssetTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahwal\Music\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Collage\magang\asset_monitoring_web\public\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C02BBE-E091-4A69-8A8E-C27D0FE3E81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578FB56D-DBF8-4658-B348-578B7D2E20A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="210" windowWidth="17385" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Import Aset" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>nama kolom</t>
   </si>
@@ -134,6 +134,33 @@
   </si>
   <si>
     <t>*Wajib Diisi : ID master aset harus berupa angka positif</t>
+  </si>
+  <si>
+    <t>*Nama Brand</t>
+  </si>
+  <si>
+    <t>Lenovo</t>
+  </si>
+  <si>
+    <t>*Wajib Diisi : Data harus sama dengan di menu brand</t>
+  </si>
+  <si>
+    <t>Nama Merk</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Philips</t>
+  </si>
+  <si>
+    <t>RJ926YU</t>
+  </si>
+  <si>
+    <t>Nama Master Aset</t>
+  </si>
+  <si>
+    <t>CT Scanner V23</t>
   </si>
 </sst>
 </file>
@@ -281,7 +308,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -333,22 +360,18 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -359,9 +382,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,101 +668,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="O1" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="F2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="16">
+      <c r="G2" s="16">
         <v>5000000</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="H2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="16">
+      <c r="K2" s="16">
         <v>5000000</v>
       </c>
-      <c r="J2" s="15">
+      <c r="L2" s="15">
         <v>500000</v>
       </c>
-      <c r="K2" s="15">
+      <c r="M2" s="15">
         <v>60</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="N2" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="20">
+      <c r="O2" s="20">
         <v>1234</v>
       </c>
     </row>
@@ -753,26 +791,26 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="82.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="82.5546875" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="28"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7" t="s">
         <v>0</v>
@@ -787,7 +825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="12" t="s">
         <v>4</v>
@@ -800,7 +838,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
@@ -812,131 +850,149 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="15" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="11"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="28">
+      <c r="C8" s="25"/>
+      <c r="D8" s="26">
         <v>45398</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E8" s="24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="25" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22">
+      <c r="C9" s="21"/>
+      <c r="D9" s="21">
         <v>500000</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E9" s="23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="25" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="18" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E11" s="23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22" t="s">
+      <c r="C12" s="21"/>
+      <c r="D12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="25" t="s">
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22">
+      <c r="C13" s="21"/>
+      <c r="D13" s="21">
         <v>500000</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E13" s="23" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22">
+      <c r="C14" s="21"/>
+      <c r="D14" s="21">
         <v>500000</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E14" s="23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="29" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22">
+      <c r="C15" s="21"/>
+      <c r="D15" s="21">
         <v>60</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="29" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="30">
+      <c r="C16" s="21"/>
+      <c r="D16" s="27">
         <v>45398</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="29" t="s">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22">
+      <c r="C17" s="21"/>
+      <c r="D17" s="21">
         <v>1234</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>33</v>
       </c>
     </row>
